--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9240"/>
+  <dimension ref="A1:B9241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74420,6 +74420,14 @@
       </c>
       <c r="B9240" t="inlineStr"/>
     </row>
+    <row r="9241">
+      <c r="A9241" t="inlineStr">
+        <is>
+          <t>m (920nm to 950nm)</t>
+        </is>
+      </c>
+      <c r="B9241" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9241"/>
+  <dimension ref="A1:B9243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74428,6 +74428,22 @@
       </c>
       <c r="B9241" t="inlineStr"/>
     </row>
+    <row r="9242">
+      <c r="A9242" t="inlineStr">
+        <is>
+          <t>V (±15, Tracking)</t>
+        </is>
+      </c>
+      <c r="B9242" t="inlineStr"/>
+    </row>
+    <row r="9243">
+      <c r="A9243" t="inlineStr">
+        <is>
+          <t>LSB/%RH</t>
+        </is>
+      </c>
+      <c r="B9243" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9243"/>
+  <dimension ref="A1:B9244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74444,6 +74444,14 @@
       </c>
       <c r="B9243" t="inlineStr"/>
     </row>
+    <row r="9244">
+      <c r="A9244" t="inlineStr">
+        <is>
+          <t>LSB/ (°/s)</t>
+        </is>
+      </c>
+      <c r="B9244" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9244"/>
+  <dimension ref="A1:B9245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74452,6 +74452,14 @@
       </c>
       <c r="B9244" t="inlineStr"/>
     </row>
+    <row r="9245">
+      <c r="A9245" t="inlineStr">
+        <is>
+          <t>VAC (Signal)</t>
+        </is>
+      </c>
+      <c r="B9245" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9245"/>
+  <dimension ref="A1:B9246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74460,6 +74460,14 @@
       </c>
       <c r="B9245" t="inlineStr"/>
     </row>
+    <row r="9246">
+      <c r="A9246" t="inlineStr">
+        <is>
+          <t>Hz (Y, Z)</t>
+        </is>
+      </c>
+      <c r="B9246" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9246"/>
+  <dimension ref="A1:B9247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74468,6 +74468,14 @@
       </c>
       <c r="B9246" t="inlineStr"/>
     </row>
+    <row r="9247">
+      <c r="A9247" t="inlineStr">
+        <is>
+          <t>W (66W Forced Air)</t>
+        </is>
+      </c>
+      <c r="B9247" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9247"/>
+  <dimension ref="A1:B9248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74476,6 +74476,14 @@
       </c>
       <c r="B9247" t="inlineStr"/>
     </row>
+    <row r="9248">
+      <c r="A9248" t="inlineStr">
+        <is>
+          <t>V (3.8V)</t>
+        </is>
+      </c>
+      <c r="B9248" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9248"/>
+  <dimension ref="A1:B9250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Base Unit Symbol</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Multiplier Symbol</t>
         </is>
@@ -74483,6 +74471,22 @@
         </is>
       </c>
       <c r="B9248" t="inlineStr"/>
+    </row>
+    <row r="9249">
+      <c r="A9249" t="inlineStr">
+        <is>
+          <t>K (2885K to 3225K)</t>
+        </is>
+      </c>
+      <c r="B9249" t="inlineStr"/>
+    </row>
+    <row r="9250">
+      <c r="A9250" t="inlineStr">
+        <is>
+          <t>K (4735K to 5285K)</t>
+        </is>
+      </c>
+      <c r="B9250" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9250"/>
+  <dimension ref="A1:B9259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74488,6 +74488,78 @@
       </c>
       <c r="B9250" t="inlineStr"/>
     </row>
+    <row r="9251">
+      <c r="A9251" t="inlineStr">
+        <is>
+          <t>lm (27lm to 34lm)</t>
+        </is>
+      </c>
+      <c r="B9251" t="inlineStr"/>
+    </row>
+    <row r="9252">
+      <c r="A9252" t="inlineStr">
+        <is>
+          <t>lm (415lm to 480lm)</t>
+        </is>
+      </c>
+      <c r="B9252" t="inlineStr"/>
+    </row>
+    <row r="9253">
+      <c r="A9253" t="inlineStr">
+        <is>
+          <t>lm (214lm to 314lm)</t>
+        </is>
+      </c>
+      <c r="B9253" t="inlineStr"/>
+    </row>
+    <row r="9254">
+      <c r="A9254" t="inlineStr">
+        <is>
+          <t>lm (146lm to 166lm)</t>
+        </is>
+      </c>
+      <c r="B9254" t="inlineStr"/>
+    </row>
+    <row r="9255">
+      <c r="A9255" t="inlineStr">
+        <is>
+          <t>lm (140lm to 287lm)</t>
+        </is>
+      </c>
+      <c r="B9255" t="inlineStr"/>
+    </row>
+    <row r="9256">
+      <c r="A9256" t="inlineStr">
+        <is>
+          <t>lm (239lm to 312lm)</t>
+        </is>
+      </c>
+      <c r="B9256" t="inlineStr"/>
+    </row>
+    <row r="9257">
+      <c r="A9257" t="inlineStr">
+        <is>
+          <t>lm (985lm to 1321lm)</t>
+        </is>
+      </c>
+      <c r="B9257" t="inlineStr"/>
+    </row>
+    <row r="9258">
+      <c r="A9258" t="inlineStr">
+        <is>
+          <t>lm (123lm to 153lm)</t>
+        </is>
+      </c>
+      <c r="B9258" t="inlineStr"/>
+    </row>
+    <row r="9259">
+      <c r="A9259" t="inlineStr">
+        <is>
+          <t>lm (126lm to 320lm)</t>
+        </is>
+      </c>
+      <c r="B9259" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9259"/>
+  <dimension ref="A1:B9260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74560,6 +74560,14 @@
       </c>
       <c r="B9259" t="inlineStr"/>
     </row>
+    <row r="9260">
+      <c r="A9260" t="inlineStr">
+        <is>
+          <t>A (AC/DC) per Contact</t>
+        </is>
+      </c>
+      <c r="B9260" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9260"/>
+  <dimension ref="A1:B9261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74568,6 +74568,14 @@
       </c>
       <c r="B9260" t="inlineStr"/>
     </row>
+    <row r="9261">
+      <c r="A9261" t="inlineStr">
+        <is>
+          <t>m (627nm to 632nm)</t>
+        </is>
+      </c>
+      <c r="B9261" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9261"/>
+  <dimension ref="A1:B9262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74576,6 +74576,14 @@
       </c>
       <c r="B9261" t="inlineStr"/>
     </row>
+    <row r="9262">
+      <c r="A9262" t="inlineStr">
+        <is>
+          <t>lm (1750lm to 2050lm)</t>
+        </is>
+      </c>
+      <c r="B9262" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9262"/>
+  <dimension ref="A1:B9263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74584,6 +74584,14 @@
       </c>
       <c r="B9262" t="inlineStr"/>
     </row>
+    <row r="9263">
+      <c r="A9263" t="inlineStr">
+        <is>
+          <t>lm (1050lm to 1230lm)</t>
+        </is>
+      </c>
+      <c r="B9263" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9263"/>
+  <dimension ref="A1:B9270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74592,6 +74592,62 @@
       </c>
       <c r="B9263" t="inlineStr"/>
     </row>
+    <row r="9264">
+      <c r="A9264" t="inlineStr">
+        <is>
+          <t>lm (440lm to 465lm)</t>
+        </is>
+      </c>
+      <c r="B9264" t="inlineStr"/>
+    </row>
+    <row r="9265">
+      <c r="A9265" t="inlineStr">
+        <is>
+          <t>lm (48lm to 64lm)</t>
+        </is>
+      </c>
+      <c r="B9265" t="inlineStr"/>
+    </row>
+    <row r="9266">
+      <c r="A9266" t="inlineStr">
+        <is>
+          <t>lm (5lm to 14lm)</t>
+        </is>
+      </c>
+      <c r="B9266" t="inlineStr"/>
+    </row>
+    <row r="9267">
+      <c r="A9267" t="inlineStr">
+        <is>
+          <t>lm (3195lm to 3400lm)</t>
+        </is>
+      </c>
+      <c r="B9267" t="inlineStr"/>
+    </row>
+    <row r="9268">
+      <c r="A9268" t="inlineStr">
+        <is>
+          <t>lm (12lm to 24lm)</t>
+        </is>
+      </c>
+      <c r="B9268" t="inlineStr"/>
+    </row>
+    <row r="9269">
+      <c r="A9269" t="inlineStr">
+        <is>
+          <t>lm (53lm to 76lm)</t>
+        </is>
+      </c>
+      <c r="B9269" t="inlineStr"/>
+    </row>
+    <row r="9270">
+      <c r="A9270" t="inlineStr">
+        <is>
+          <t>lm (53lm to 82lm)</t>
+        </is>
+      </c>
+      <c r="B9270" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9270"/>
+  <dimension ref="A1:B9271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74648,6 +74648,14 @@
       </c>
       <c r="B9270" t="inlineStr"/>
     </row>
+    <row r="9271">
+      <c r="A9271" t="inlineStr">
+        <is>
+          <t>B PSARM</t>
+        </is>
+      </c>
+      <c r="B9271" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9271"/>
+  <dimension ref="A1:B9275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74656,6 +74656,38 @@
       </c>
       <c r="B9271" t="inlineStr"/>
     </row>
+    <row r="9272">
+      <c r="A9272" t="inlineStr">
+        <is>
+          <t>W (167W Forced Air)</t>
+        </is>
+      </c>
+      <c r="B9272" t="inlineStr"/>
+    </row>
+    <row r="9273">
+      <c r="A9273" t="inlineStr">
+        <is>
+          <t>lm (430lm to 510lm)</t>
+        </is>
+      </c>
+      <c r="B9273" t="inlineStr"/>
+    </row>
+    <row r="9274">
+      <c r="A9274" t="inlineStr">
+        <is>
+          <t>lm (410lm to 510lm)</t>
+        </is>
+      </c>
+      <c r="B9274" t="inlineStr"/>
+    </row>
+    <row r="9275">
+      <c r="A9275" t="inlineStr">
+        <is>
+          <t>lm (430lm to 535lm)</t>
+        </is>
+      </c>
+      <c r="B9275" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9275"/>
+  <dimension ref="A1:B9276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74688,6 +74688,14 @@
       </c>
       <c r="B9275" t="inlineStr"/>
     </row>
+    <row r="9276">
+      <c r="A9276" t="inlineStr">
+        <is>
+          <t>VAC (1PH to 2PH)</t>
+        </is>
+      </c>
+      <c r="B9276" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9276"/>
+  <dimension ref="A1:B9279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74696,6 +74696,30 @@
       </c>
       <c r="B9276" t="inlineStr"/>
     </row>
+    <row r="9277">
+      <c r="A9277" t="inlineStr">
+        <is>
+          <t>lm (380lm to 620lm)</t>
+        </is>
+      </c>
+      <c r="B9277" t="inlineStr"/>
+    </row>
+    <row r="9278">
+      <c r="A9278" t="inlineStr">
+        <is>
+          <t>lm (340lm to 620lm)</t>
+        </is>
+      </c>
+      <c r="B9278" t="inlineStr"/>
+    </row>
+    <row r="9279">
+      <c r="A9279" t="inlineStr">
+        <is>
+          <t>lm (480lm to 620lm)</t>
+        </is>
+      </c>
+      <c r="B9279" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9279"/>
+  <dimension ref="A1:B9281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74720,6 +74720,22 @@
       </c>
       <c r="B9279" t="inlineStr"/>
     </row>
+    <row r="9280">
+      <c r="A9280" t="inlineStr">
+        <is>
+          <t>lm (42lm to 66lm)</t>
+        </is>
+      </c>
+      <c r="B9280" t="inlineStr"/>
+    </row>
+    <row r="9281">
+      <c r="A9281" t="inlineStr">
+        <is>
+          <t>lm (42lm to 61lm)</t>
+        </is>
+      </c>
+      <c r="B9281" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9281"/>
+  <dimension ref="A1:B9288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74736,6 +74736,62 @@
       </c>
       <c r="B9281" t="inlineStr"/>
     </row>
+    <row r="9282">
+      <c r="A9282" t="inlineStr">
+        <is>
+          <t>°C (±0.688°C)</t>
+        </is>
+      </c>
+      <c r="B9282" t="inlineStr"/>
+    </row>
+    <row r="9283">
+      <c r="A9283" t="inlineStr">
+        <is>
+          <t>°C (-10°C to 148.9°C)</t>
+        </is>
+      </c>
+      <c r="B9283" t="inlineStr"/>
+    </row>
+    <row r="9284">
+      <c r="A9284" t="inlineStr">
+        <is>
+          <t>°C (-4.4°C)</t>
+        </is>
+      </c>
+      <c r="B9284" t="inlineStr"/>
+    </row>
+    <row r="9285">
+      <c r="A9285" t="inlineStr">
+        <is>
+          <t>°C (0°C)</t>
+        </is>
+      </c>
+      <c r="B9285" t="inlineStr"/>
+    </row>
+    <row r="9286">
+      <c r="A9286" t="inlineStr">
+        <is>
+          <t>°C (125°C to 150°C)</t>
+        </is>
+      </c>
+      <c r="B9286" t="inlineStr"/>
+    </row>
+    <row r="9287">
+      <c r="A9287" t="inlineStr">
+        <is>
+          <t>°C (-3.5°C, ±3°C)</t>
+        </is>
+      </c>
+      <c r="B9287" t="inlineStr"/>
+    </row>
+    <row r="9288">
+      <c r="A9288" t="inlineStr">
+        <is>
+          <t>°C (5°C)</t>
+        </is>
+      </c>
+      <c r="B9288" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9288"/>
+  <dimension ref="A1:B9290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74792,6 +74792,22 @@
       </c>
       <c r="B9288" t="inlineStr"/>
     </row>
+    <row r="9289">
+      <c r="A9289" t="inlineStr">
+        <is>
+          <t>°C (-2°C, 4°C)</t>
+        </is>
+      </c>
+      <c r="B9289" t="inlineStr"/>
+    </row>
+    <row r="9290">
+      <c r="A9290" t="inlineStr">
+        <is>
+          <t>°C (-3.5°C, 3°C)</t>
+        </is>
+      </c>
+      <c r="B9290" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9290"/>
+  <dimension ref="A1:B9291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74808,6 +74808,14 @@
       </c>
       <c r="B9290" t="inlineStr"/>
     </row>
+    <row r="9291">
+      <c r="A9291" t="inlineStr">
+        <is>
+          <t>°C (-30°C)</t>
+        </is>
+      </c>
+      <c r="B9291" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9291"/>
+  <dimension ref="A1:B9293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74816,6 +74816,22 @@
       </c>
       <c r="B9291" t="inlineStr"/>
     </row>
+    <row r="9292">
+      <c r="A9292" t="inlineStr">
+        <is>
+          <t>gal/h</t>
+        </is>
+      </c>
+      <c r="B9292" t="inlineStr"/>
+    </row>
+    <row r="9293">
+      <c r="A9293" t="inlineStr">
+        <is>
+          <t>(1800K to 6500K) 3-Step MacAdam Ellipse</t>
+        </is>
+      </c>
+      <c r="B9293" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9293"/>
+  <dimension ref="A1:B9294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74832,6 +74832,14 @@
       </c>
       <c r="B9293" t="inlineStr"/>
     </row>
+    <row r="9294">
+      <c r="A9294" t="inlineStr">
+        <is>
+          <t>K (1800K to 6500K) 3-Step MacAdam Ellipse</t>
+        </is>
+      </c>
+      <c r="B9294" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9294"/>
+  <dimension ref="A1:B9295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74840,6 +74840,14 @@
       </c>
       <c r="B9294" t="inlineStr"/>
     </row>
+    <row r="9295">
+      <c r="A9295" t="inlineStr">
+        <is>
+          <t>V (x4)</t>
+        </is>
+      </c>
+      <c r="B9295" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9295"/>
+  <dimension ref="A1:B9296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74848,6 +74848,14 @@
       </c>
       <c r="B9295" t="inlineStr"/>
     </row>
+    <row r="9296">
+      <c r="A9296" t="inlineStr">
+        <is>
+          <t>lm (164lm to 224lm)</t>
+        </is>
+      </c>
+      <c r="B9296" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9296"/>
+  <dimension ref="A1:B9297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74856,6 +74856,14 @@
       </c>
       <c r="B9296" t="inlineStr"/>
     </row>
+    <row r="9297">
+      <c r="A9297" t="inlineStr">
+        <is>
+          <t>°C, External Sensor</t>
+        </is>
+      </c>
+      <c r="B9297" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9297"/>
+  <dimension ref="A1:B9299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74864,6 +74864,22 @@
       </c>
       <c r="B9297" t="inlineStr"/>
     </row>
+    <row r="9298">
+      <c r="A9298" t="inlineStr">
+        <is>
+          <t>°C (25°C to 125°C)</t>
+        </is>
+      </c>
+      <c r="B9298" t="inlineStr"/>
+    </row>
+    <row r="9299">
+      <c r="A9299" t="inlineStr">
+        <is>
+          <t>°C (±0.25°C)</t>
+        </is>
+      </c>
+      <c r="B9299" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9299"/>
+  <dimension ref="A1:B9300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74880,6 +74880,14 @@
       </c>
       <c r="B9299" t="inlineStr"/>
     </row>
+    <row r="9300">
+      <c r="A9300" t="inlineStr">
+        <is>
+          <t>lm (60lm to 85lm)</t>
+        </is>
+      </c>
+      <c r="B9300" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9300"/>
+  <dimension ref="A1:B9302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74888,6 +74888,22 @@
       </c>
       <c r="B9300" t="inlineStr"/>
     </row>
+    <row r="9301">
+      <c r="A9301" t="inlineStr">
+        <is>
+          <t>°C (85°C)</t>
+        </is>
+      </c>
+      <c r="B9301" t="inlineStr"/>
+    </row>
+    <row r="9302">
+      <c r="A9302" t="inlineStr">
+        <is>
+          <t>°C (-25°C to 105°C)</t>
+        </is>
+      </c>
+      <c r="B9302" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9302"/>
+  <dimension ref="A1:B9303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74904,6 +74904,14 @@
       </c>
       <c r="B9302" t="inlineStr"/>
     </row>
+    <row r="9303">
+      <c r="A9303" t="inlineStr">
+        <is>
+          <t>m (485nm to 495nm)</t>
+        </is>
+      </c>
+      <c r="B9303" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9303"/>
+  <dimension ref="A1:B9305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74912,6 +74912,22 @@
       </c>
       <c r="B9303" t="inlineStr"/>
     </row>
+    <row r="9304">
+      <c r="A9304" t="inlineStr">
+        <is>
+          <t>lm (230lm to 300lm)</t>
+        </is>
+      </c>
+      <c r="B9304" t="inlineStr"/>
+    </row>
+    <row r="9305">
+      <c r="A9305" t="inlineStr">
+        <is>
+          <t>K (8000K to 20000K)</t>
+        </is>
+      </c>
+      <c r="B9305" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9305"/>
+  <dimension ref="A1:B9306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74928,6 +74928,14 @@
       </c>
       <c r="B9305" t="inlineStr"/>
     </row>
+    <row r="9306">
+      <c r="A9306" t="inlineStr">
+        <is>
+          <t>lm (949lm to 1180lm)</t>
+        </is>
+      </c>
+      <c r="B9306" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9306"/>
+  <dimension ref="A1:B9309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74936,6 +74936,30 @@
       </c>
       <c r="B9306" t="inlineStr"/>
     </row>
+    <row r="9307">
+      <c r="A9307" t="inlineStr">
+        <is>
+          <t>lm (594lm to 669lm)</t>
+        </is>
+      </c>
+      <c r="B9307" t="inlineStr"/>
+    </row>
+    <row r="9308">
+      <c r="A9308" t="inlineStr">
+        <is>
+          <t>lm (669lm to 754lm)</t>
+        </is>
+      </c>
+      <c r="B9308" t="inlineStr"/>
+    </row>
+    <row r="9309">
+      <c r="A9309" t="inlineStr">
+        <is>
+          <t>m (611nm to 624nm)</t>
+        </is>
+      </c>
+      <c r="B9309" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9309"/>
+  <dimension ref="A1:B9312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74960,6 +74960,30 @@
       </c>
       <c r="B9309" t="inlineStr"/>
     </row>
+    <row r="9310">
+      <c r="A9310" t="inlineStr">
+        <is>
+          <t>V (1.85V)</t>
+        </is>
+      </c>
+      <c r="B9310" t="inlineStr"/>
+    </row>
+    <row r="9311">
+      <c r="A9311" t="inlineStr">
+        <is>
+          <t>V (3.45V)</t>
+        </is>
+      </c>
+      <c r="B9311" t="inlineStr"/>
+    </row>
+    <row r="9312">
+      <c r="A9312" t="inlineStr">
+        <is>
+          <t>V (1.25V)</t>
+        </is>
+      </c>
+      <c r="B9312" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9312"/>
+  <dimension ref="A1:B9314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74984,6 +74984,22 @@
       </c>
       <c r="B9312" t="inlineStr"/>
     </row>
+    <row r="9313">
+      <c r="A9313" t="inlineStr">
+        <is>
+          <t>lm (370lm to 390lm)</t>
+        </is>
+      </c>
+      <c r="B9313" t="inlineStr"/>
+    </row>
+    <row r="9314">
+      <c r="A9314" t="inlineStr">
+        <is>
+          <t>lm (265lm to 310lm)</t>
+        </is>
+      </c>
+      <c r="B9314" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9314"/>
+  <dimension ref="A1:B9315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75000,6 +75000,14 @@
       </c>
       <c r="B9314" t="inlineStr"/>
     </row>
+    <row r="9315">
+      <c r="A9315" t="inlineStr">
+        <is>
+          <t>lm (370lm to 380lm)</t>
+        </is>
+      </c>
+      <c r="B9315" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9315"/>
+  <dimension ref="A1:B9318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75008,6 +75008,30 @@
       </c>
       <c r="B9315" t="inlineStr"/>
     </row>
+    <row r="9316">
+      <c r="A9316" t="inlineStr">
+        <is>
+          <t>lm (435lm to 510lm)</t>
+        </is>
+      </c>
+      <c r="B9316" t="inlineStr"/>
+    </row>
+    <row r="9317">
+      <c r="A9317" t="inlineStr">
+        <is>
+          <t>lm (415lm to 485lm)</t>
+        </is>
+      </c>
+      <c r="B9317" t="inlineStr"/>
+    </row>
+    <row r="9318">
+      <c r="A9318" t="inlineStr">
+        <is>
+          <t>lm (415lm to 460lm)</t>
+        </is>
+      </c>
+      <c r="B9318" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9318"/>
+  <dimension ref="A1:B9319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75032,6 +75032,14 @@
       </c>
       <c r="B9318" t="inlineStr"/>
     </row>
+    <row r="9319">
+      <c r="A9319" t="inlineStr">
+        <is>
+          <t>lm (212lm to 234lm)</t>
+        </is>
+      </c>
+      <c r="B9319" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9319"/>
+  <dimension ref="A1:B9334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75040,6 +75040,126 @@
       </c>
       <c r="B9319" t="inlineStr"/>
     </row>
+    <row r="9320">
+      <c r="A9320" t="inlineStr">
+        <is>
+          <t>lm (200lm to 290lm)</t>
+        </is>
+      </c>
+      <c r="B9320" t="inlineStr"/>
+    </row>
+    <row r="9321">
+      <c r="A9321" t="inlineStr">
+        <is>
+          <t>lm (270lm to 350lm)</t>
+        </is>
+      </c>
+      <c r="B9321" t="inlineStr"/>
+    </row>
+    <row r="9322">
+      <c r="A9322" t="inlineStr">
+        <is>
+          <t>lm (250lm to 350lm)</t>
+        </is>
+      </c>
+      <c r="B9322" t="inlineStr"/>
+    </row>
+    <row r="9323">
+      <c r="A9323" t="inlineStr">
+        <is>
+          <t>lm (310lm to 410lm)</t>
+        </is>
+      </c>
+      <c r="B9323" t="inlineStr"/>
+    </row>
+    <row r="9324">
+      <c r="A9324" t="inlineStr">
+        <is>
+          <t>lm (170lm to 250lm)</t>
+        </is>
+      </c>
+      <c r="B9324" t="inlineStr"/>
+    </row>
+    <row r="9325">
+      <c r="A9325" t="inlineStr">
+        <is>
+          <t>lm (290lm to 390lm)</t>
+        </is>
+      </c>
+      <c r="B9325" t="inlineStr"/>
+    </row>
+    <row r="9326">
+      <c r="A9326" t="inlineStr">
+        <is>
+          <t>lm (260lm to 350lm)</t>
+        </is>
+      </c>
+      <c r="B9326" t="inlineStr"/>
+    </row>
+    <row r="9327">
+      <c r="A9327" t="inlineStr">
+        <is>
+          <t>lm (230lm to 330lm)</t>
+        </is>
+      </c>
+      <c r="B9327" t="inlineStr"/>
+    </row>
+    <row r="9328">
+      <c r="A9328" t="inlineStr">
+        <is>
+          <t>lm (315lm to 455lm)</t>
+        </is>
+      </c>
+      <c r="B9328" t="inlineStr"/>
+    </row>
+    <row r="9329">
+      <c r="A9329" t="inlineStr">
+        <is>
+          <t>lm (260lm to 360lm)</t>
+        </is>
+      </c>
+      <c r="B9329" t="inlineStr"/>
+    </row>
+    <row r="9330">
+      <c r="A9330" t="inlineStr">
+        <is>
+          <t>lm (190lm to 280lm)</t>
+        </is>
+      </c>
+      <c r="B9330" t="inlineStr"/>
+    </row>
+    <row r="9331">
+      <c r="A9331" t="inlineStr">
+        <is>
+          <t>lm (300lm to 390lm)</t>
+        </is>
+      </c>
+      <c r="B9331" t="inlineStr"/>
+    </row>
+    <row r="9332">
+      <c r="A9332" t="inlineStr">
+        <is>
+          <t>lm (330lm to 430lm)</t>
+        </is>
+      </c>
+      <c r="B9332" t="inlineStr"/>
+    </row>
+    <row r="9333">
+      <c r="A9333" t="inlineStr">
+        <is>
+          <t>lm (210lm to 320lm)</t>
+        </is>
+      </c>
+      <c r="B9333" t="inlineStr"/>
+    </row>
+    <row r="9334">
+      <c r="A9334" t="inlineStr">
+        <is>
+          <t>lm (240lm to 350lm)</t>
+        </is>
+      </c>
+      <c r="B9334" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9334"/>
+  <dimension ref="A1:B9335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75160,6 +75160,14 @@
       </c>
       <c r="B9334" t="inlineStr"/>
     </row>
+    <row r="9335">
+      <c r="A9335" t="inlineStr">
+        <is>
+          <t>K (5700K to 6700K)</t>
+        </is>
+      </c>
+      <c r="B9335" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9335"/>
+  <dimension ref="A1:B9338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75168,6 +75168,30 @@
       </c>
       <c r="B9335" t="inlineStr"/>
     </row>
+    <row r="9336">
+      <c r="A9336" t="inlineStr">
+        <is>
+          <t>lm (7100lm to 9700lm)</t>
+        </is>
+      </c>
+      <c r="B9336" t="inlineStr"/>
+    </row>
+    <row r="9337">
+      <c r="A9337" t="inlineStr">
+        <is>
+          <t>°C (-5°C, +1°C)</t>
+        </is>
+      </c>
+      <c r="B9337" t="inlineStr"/>
+    </row>
+    <row r="9338">
+      <c r="A9338" t="inlineStr">
+        <is>
+          <t>°C (-4°C, +6°C)</t>
+        </is>
+      </c>
+      <c r="B9338" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9338"/>
+  <dimension ref="A1:B9339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75192,6 +75192,14 @@
       </c>
       <c r="B9338" t="inlineStr"/>
     </row>
+    <row r="9339">
+      <c r="A9339" t="inlineStr">
+        <is>
+          <t>lm (125lm to 176lm)</t>
+        </is>
+      </c>
+      <c r="B9339" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9339"/>
+  <dimension ref="A1:B9340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75200,6 +75200,14 @@
       </c>
       <c r="B9339" t="inlineStr"/>
     </row>
+    <row r="9340">
+      <c r="A9340" t="inlineStr">
+        <is>
+          <t>(±25g)</t>
+        </is>
+      </c>
+      <c r="B9340" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9340"/>
+  <dimension ref="A1:B9342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75208,6 +75208,22 @@
       </c>
       <c r="B9340" t="inlineStr"/>
     </row>
+    <row r="9341">
+      <c r="A9341" t="inlineStr">
+        <is>
+          <t>A (AC/DC) Power</t>
+        </is>
+      </c>
+      <c r="B9341" t="inlineStr"/>
+    </row>
+    <row r="9342">
+      <c r="A9342" t="inlineStr">
+        <is>
+          <t>A (AC/DC) Signal</t>
+        </is>
+      </c>
+      <c r="B9342" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9342"/>
+  <dimension ref="A1:B9343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75224,6 +75224,14 @@
       </c>
       <c r="B9342" t="inlineStr"/>
     </row>
+    <row r="9343">
+      <c r="A9343" t="inlineStr">
+        <is>
+          <t>W (129W Forced Air)</t>
+        </is>
+      </c>
+      <c r="B9343" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
